--- a/TABLAS/Tablas_cuerpo.xlsx
+++ b/TABLAS/Tablas_cuerpo.xlsx
@@ -410,7 +410,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8 067</t>
+          <t>8 066</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -420,22 +420,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2 368</t>
+          <t>2 364</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3 630</t>
+          <t>3 626</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1 608</t>
+          <t>1 607</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1 349</t>
+          <t>1 348</t>
         </is>
       </c>
     </row>
@@ -462,12 +462,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2 789</t>
+          <t>2 786</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4 183</t>
+          <t>4 181</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -546,12 +546,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1 582</t>
+          <t>1 568</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2 293</t>
+          <t>2 285</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>25 089</t>
+          <t>25 088</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -588,22 +588,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7 756</t>
+          <t>7 735</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>11 611</t>
+          <t>11 597</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>5 204</t>
+          <t>5 203</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4 389</t>
+          <t>4 388</t>
         </is>
       </c>
     </row>
@@ -659,22 +659,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7 756</t>
+          <t>7 735</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65,8</t>
+          <t>65,9</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>63,6–67,9</t>
+          <t>63,8–68,1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>64,2</t>
+          <t>64,4</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11 611</t>
+          <t>11 597</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>40,0–43,7</t>
+          <t>40,1–43,8</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -713,7 +713,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5 204</t>
+          <t>5 203</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -740,17 +740,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4 389</t>
+          <t>4 388</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>63,8</t>
+          <t>64,0</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>61,1–66,4</t>
+          <t>61,3–66,7</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -767,22 +767,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4 389</t>
+          <t>4 388</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>40,4</t>
+          <t>40,6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>37,6–43,2</t>
+          <t>37,8–43,5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>42,0</t>
+          <t>42,1</t>
         </is>
       </c>
     </row>

--- a/TABLAS/Tablas_cuerpo.xlsx
+++ b/TABLAS/Tablas_cuerpo.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>64,4</t>
+          <t>65,2</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>40,9</t>
+          <t>41,7</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>79,7</t>
+          <t>80,0</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>65,0</t>
+          <t>64,6</t>
         </is>
       </c>
     </row>
@@ -782,7 +782,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>42,1</t>
+          <t>41,6</t>
         </is>
       </c>
     </row>
